--- a/Result/profitability/5309.xlsx
+++ b/Result/profitability/5309.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.01875000000000003</v>
+        <v>0.003749999999999976</v>
       </c>
       <c r="N2" t="n">
-        <v>22.3675</v>
+        <v>22.43</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02625000000000003</v>
+        <v>-0.05125000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>20.645</v>
+        <v>20.2125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05250000000000003</v>
+        <v>-0.07000000000000003</v>
       </c>
       <c r="N4" t="n">
-        <v>18.7825</v>
+        <v>18.60875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1025</v>
+        <v>-0.1075</v>
       </c>
       <c r="N5" t="n">
-        <v>16.655</v>
+        <v>16.36625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.10625</v>
+        <v>-0.09625000000000004</v>
       </c>
       <c r="N6" t="n">
-        <v>15.59</v>
+        <v>15.70625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.115</v>
+        <v>-0.1475</v>
       </c>
       <c r="N7" t="n">
-        <v>14.3925</v>
+        <v>14.1025</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.13875</v>
+        <v>-0.1525000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>13.66125</v>
+        <v>13.3325</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>897</v>
+      </c>
+      <c r="D75" t="n">
+        <v>698</v>
+      </c>
+      <c r="E75" t="n">
+        <v>199</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-65</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-7.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>44</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04124999999999997</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.565</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.222222222222222</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.629999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1057924376508447</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.309999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09413202933985321</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
